--- a/plantilla_instituciones.xlsx
+++ b/plantilla_instituciones.xlsx
@@ -1265,7 +1265,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="es-CR" sz="1200" b="1"/>
-              <a:t>Posición: tolerancia y apetito</a:t>
+              <a:t>Posición: tolerancia y apetito (líneas de corte del perfil)</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1541,6 +1541,68 @@
           <c:yVal>
             <c:numRef>
               <c:f>'Datos'!$C$7</c:f>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Datos'!$L$1</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="918042"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Datos'!$L$2:$L$3</c:f>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Datos'!$M$2:$M$3</c:f>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Datos'!$N$1</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="918042"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Datos'!$N$2:$N$3</c:f>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Datos'!$O$2:$O$3</c:f>
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>

--- a/plantilla_instituciones.xlsx
+++ b/plantilla_instituciones.xlsx
@@ -966,6 +966,142 @@
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="2B3014"/>
+              </a:solidFill>
+              <a:ln w="15875">
+                <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:srgbClr val="2B3014"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr sz="900">
+                    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                      <a:srgbClr val="2B3014"/>
+                    </a:solidFill>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-CR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="b"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Datos'!$I$5</c:f>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Datos'!$J$5</c:f>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Datos'!$H$6</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="2B3014"/>
+              </a:solidFill>
+              <a:ln w="15875">
+                <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:srgbClr val="2B3014"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr sz="900">
+                    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                      <a:srgbClr val="2B3014"/>
+                    </a:solidFill>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-CR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="b"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Datos'!$I$6</c:f>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Datos'!$J$6</c:f>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Datos'!$H$7</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
             <c:size val="12"/>
             <c:spPr>
               <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
@@ -1007,22 +1143,22 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'Datos'!$I$5</c:f>
+              <c:f>'Datos'!$I$7</c:f>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Datos'!$J$5</c:f>
+              <c:f>'Datos'!$J$7</c:f>
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
         <c:ser>
-          <c:idx val="5"/>
-          <c:order val="5"/>
+          <c:idx val="7"/>
+          <c:order val="7"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Datos'!$H$7</c:f>
+              <c:f>'Datos'!$H$9</c:f>
             </c:strRef>
           </c:tx>
           <c:spPr>
@@ -1038,22 +1174,22 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Datos'!$I$7:$I$9</c:f>
+              <c:f>'Datos'!$I$9:$I$11</c:f>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Datos'!$J$7:$J$9</c:f>
+              <c:f>'Datos'!$J$9:$J$11</c:f>
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
         <c:ser>
-          <c:idx val="6"/>
-          <c:order val="6"/>
+          <c:idx val="8"/>
+          <c:order val="8"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Datos'!$H$6</c:f>
+              <c:f>'Datos'!$H$8</c:f>
             </c:strRef>
           </c:tx>
           <c:spPr>
@@ -1106,12 +1242,12 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'Datos'!$I$6</c:f>
+              <c:f>'Datos'!$I$8</c:f>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Datos'!$J$6</c:f>
+              <c:f>'Datos'!$J$8</c:f>
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
@@ -1511,6 +1647,63 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
+              <c:f>'Datos'!$A$13</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr sz="900">
+                    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                      <a:srgbClr val="6E7356"/>
+                    </a:solidFill>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-CR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Datos'!$B$13</c:f>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Datos'!$C$13</c:f>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
               <c:f>'Datos'!$A$7</c:f>
             </c:strRef>
           </c:tx>
@@ -1546,8 +1739,8 @@
           <c:smooth val="0"/>
         </c:ser>
         <c:ser>
-          <c:idx val="5"/>
-          <c:order val="5"/>
+          <c:idx val="6"/>
+          <c:order val="6"/>
           <c:tx>
             <c:strRef>
               <c:f>'Datos'!$L$1</c:f>
@@ -1577,8 +1770,8 @@
           <c:smooth val="0"/>
         </c:ser>
         <c:ser>
-          <c:idx val="6"/>
-          <c:order val="6"/>
+          <c:idx val="7"/>
+          <c:order val="7"/>
           <c:tx>
             <c:strRef>
               <c:f>'Datos'!$N$1</c:f>
@@ -1603,6 +1796,68 @@
           <c:yVal>
             <c:numRef>
               <c:f>'Datos'!$O$2:$O$3</c:f>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="8"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Datos'!$P$1</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="918042"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Datos'!$P$2:$P$3</c:f>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Datos'!$Q$2:$Q$3</c:f>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="9"/>
+          <c:order val="9"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Datos'!$R$1</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="918042"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Datos'!$R$2:$R$3</c:f>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Datos'!$S$2:$S$3</c:f>
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>

--- a/plantilla_instituciones.xlsx
+++ b/plantilla_instituciones.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,16 +40,101 @@
       <b val="1"/>
       <sz val="11.5"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="16"/>
+      <color rgb="FF2B3014"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="9.5"/>
+      <color rgb="FF5A5E44"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10.5"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+      <color rgb="FF918042"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1E2010"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="9.5"/>
+      <color rgb="FF2B3014"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+      <color rgb="FF141709"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="9"/>
+      <color rgb="FF6B6E55"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2B3014"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF918042"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF8E5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF1E6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4F5EE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -63,11 +148,49 @@
     <border>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9DDCB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF2B3014"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF918042"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9DDCB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9DDCB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -81,6 +204,60 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="4" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="4" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="6" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="5" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>

--- a/plantilla_instituciones.xlsx
+++ b/plantilla_instituciones.xlsx
@@ -18,7 +18,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="170" formatCode="0.0"/>
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
   <fonts count="12">
@@ -190,7 +191,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -257,6 +258,18 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="4" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
